--- a/admin-bulk-register-template.xlsx
+++ b/admin-bulk-register-template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="신청자명단" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참가자명단" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -96,7 +96,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -467,162 +467,192 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>참가신청자 일괄 등록 양식 (관리자용)</t>
+          <t>참가자 명단 업로드 양식 (관리자용)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>대회</t>
+          <t>배번</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>종목/유형</t>
+          <t>배번색</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>희망일(선택)</t>
+          <t>출발위치</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>학교명</t>
+          <t>참가자 구분</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>학년/구분</t>
+          <t>소속</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>대표자</t>
+          <t>학년</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>연락처</t>
+          <t>반</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>참가자명단(선택)</t>
+          <t>성명</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>비고(선택)</t>
+          <t>성별</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>트랙마라톤 축제</t>
-        </is>
+      <c r="A4" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>3km 마라톤 (초등학교 4·5·6학년 및 초등학교 교직원부)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
+          <t>노랑</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>의림문</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>제천OO초등학교</t>
+          <t>학생</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>5학년</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>홍길동</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>010-0000-0000</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+          <t>홍광초등학교</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>박시율</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>충북교육감기 육상대회</t>
-        </is>
+      <c r="A5" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>숙박형</t>
+          <t>노랑</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>11.9(월)~11.10(화)</t>
+          <t>의림문</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>제천OO중학교</t>
+          <t>학생</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2학년</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>010-1111-2222</t>
-        </is>
+          <t>홍광초등학교</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>이영희, 박민수</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
+          <t>박신향</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>노랑</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>의림문</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>교직원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>홍광초등학교</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>최준</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="n"/>
@@ -1053,21 +1083,145 @@
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
     </row>
-    <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>작성 안내: '대회'는 '트랙마라톤 축제' 또는 '충북교육감기 육상대회' 중 정확히 입력(드롭다운 권장). '종목/유형'은 실제 신청 종목 또는 숙박형/1일형 등을 입력. 헤더 행(3행)은 수정하지 마세요. 이 양식으로 업로드된 내용은 모두 '개인 신청' 건으로 등록됩니다.</t>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="n"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="4" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="4" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="4" t="n"/>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>작성 안내: '소속'과 '성명'은 필수입니다. 업로드 화면에서 '대회'와 '종목/유형'을 별도로 선택한 뒤 이 파일을 올리면, 여기 적힌 모든 참가자가 그 대회/종목으로 한 번에 등록됩니다. 헤더 행(3행)은 수정하지 마세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A58:I58"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="A4:A45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 대회명" error="정확한 대회명을 선택해 주세요." type="list">
-      <formula1>"트랙마라톤 축제,충북교육감기 육상대회"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="D4:D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"학생,교직원"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I4:I56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"남,여"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
